--- a/artfynd/A 32743-2020 artfynd.xlsx
+++ b/artfynd/A 32743-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32743-2020 artfynd.xlsx
+++ b/artfynd/A 32743-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +907,220 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122539511</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78652</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nordkölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>482952</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6935125</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122537650</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91097</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>658</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nordkölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>482931</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6935127</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32743-2020 artfynd.xlsx
+++ b/artfynd/A 32743-2020 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122539511</v>
+        <v>122537650</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
+        <v>91110</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482952</v>
+        <v>482931</v>
       </c>
       <c r="R4" t="n">
-        <v>6935125</v>
+        <v>6935127</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122537650</v>
+        <v>122569910</v>
       </c>
       <c r="B5" t="n">
-        <v>91097</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482931</v>
+        <v>482952</v>
       </c>
       <c r="R5" t="n">
-        <v>6935127</v>
+        <v>6935125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 32743-2020 artfynd.xlsx
+++ b/artfynd/A 32743-2020 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>122537650</v>
       </c>
       <c r="B4" t="n">
-        <v>91110</v>
+        <v>91123</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 32743-2020 artfynd.xlsx
+++ b/artfynd/A 32743-2020 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>122537650</v>
       </c>
       <c r="B4" t="n">
-        <v>91123</v>
+        <v>91124</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 32743-2020 artfynd.xlsx
+++ b/artfynd/A 32743-2020 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>122537650</v>
       </c>
       <c r="B4" t="n">
-        <v>91231</v>
+        <v>91235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>122569910</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
